--- a/src/test/output_test/Specific_Regions/Region_-200_200_0/Stats_specific_-200_200_0.xlsx
+++ b/src/test/output_test/Specific_Regions/Region_-200_200_0/Stats_specific_-200_200_0.xlsx
@@ -522,22 +522,22 @@
         <v>23</v>
       </c>
       <c r="C2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0.97699999809265</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>3</v>
       </c>
       <c r="F2">
-        <v>100602</v>
+        <v>100631</v>
       </c>
       <c r="G2">
-        <v>288082.5782491806</v>
+        <v>301893</v>
       </c>
       <c r="H2">
-        <v>288.0825782491806</v>
+        <v>301.893</v>
       </c>
       <c r="I2">
         <v>-199</v>
@@ -546,40 +546,40 @@
         <v>199</v>
       </c>
       <c r="K2">
-        <v>43.88923679449713</v>
+        <v>43.20815653228131</v>
       </c>
       <c r="L2">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="M2">
-        <v>1148</v>
+        <v>1146</v>
       </c>
       <c r="N2">
         <v>49</v>
       </c>
       <c r="O2">
-        <v>53.31210762223605</v>
+        <v>53.52990670826198</v>
       </c>
       <c r="P2">
-        <v>-1.561059920193307</v>
+        <v>-1.619120195722781</v>
       </c>
       <c r="Q2">
-        <v>4.56383645084617</v>
+        <v>4.741247196802396</v>
       </c>
       <c r="R2">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="S2">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="T2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="U2">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="V2">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
